--- a/outputs/evaluation/appendix/Appendix_G_E6_Processing_Time.xlsx
+++ b/outputs/evaluation/appendix/Appendix_G_E6_Processing_Time.xlsx
@@ -14956,7 +14956,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 4.21</t>
+          <t>Table G.1</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15187,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Table 4.22</t>
+          <t>Table G.2</t>
         </is>
       </c>
     </row>
@@ -15387,10 +15387,10 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="65" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Note. Stage times from the same sequential pass as Table 4.21. Stages 1–5 are shared by both algorithms, so their times differ only by measurement noise; the difference in total time comes from Stage 6. The remainder of the total (noise-floor estimation and bookkeeping) is not shown.</t>
+          <t>Note. Stage times from the same sequential pass as the per-slice processing times. Stages 1–5 are shared by both algorithms, so their times differ only by measurement noise; the difference in total time comes from Stage 6. The remainder of the total (noise-floor estimation and bookkeeping) is not shown.</t>
         </is>
       </c>
     </row>
